--- a/Ability stat sheet.xlsx
+++ b/Ability stat sheet.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t>No.</t>
   </si>
@@ -51,6 +51,9 @@
     <t>Damage</t>
   </si>
   <si>
+    <t>Staggering time</t>
+  </si>
+  <si>
     <t>Max reach</t>
   </si>
   <si>
@@ -93,7 +96,7 @@
     <t>Ignition uppercut</t>
   </si>
   <si>
-    <t>applier,excutioner</t>
+    <t>applier,executioner</t>
   </si>
   <si>
     <t>Aerial</t>
@@ -105,7 +108,7 @@
     <t>Sharpshooter</t>
   </si>
   <si>
-    <t>excutioner</t>
+    <t>executioner</t>
   </si>
   <si>
     <t>Ice bolt</t>
@@ -124,6 +127,9 @@
   </si>
   <si>
     <t>Double the trouble</t>
+  </si>
+  <si>
+    <t>(?)</t>
   </si>
   <si>
     <t>HP</t>
@@ -771,7 +777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -785,6 +791,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1329,17 +1338,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.99082568807339" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="8.99082568807339" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.23853211009174" customWidth="1"/>
     <col min="2" max="2" width="23.0550458715596" customWidth="1"/>
     <col min="4" max="4" width="17.9449541284404" customWidth="1"/>
     <col min="6" max="6" width="11.2201834862385" customWidth="1"/>
-    <col min="8" max="8" width="9.63302752293578" customWidth="1"/>
+    <col min="8" max="8" width="15.697247706422" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1361,273 +1370,306 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7">
+        <v>45</v>
+      </c>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7">
+        <v>35</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7">
+        <v>30</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="7">
+        <v>200</v>
+      </c>
+      <c r="G6" s="7">
+        <v>45</v>
+      </c>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7">
+        <v>50</v>
+      </c>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7">
+        <v>200</v>
+      </c>
+      <c r="G8" s="7">
+        <v>30</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7">
+        <v>35</v>
+      </c>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7">
+        <v>200</v>
+      </c>
+      <c r="G10" s="7">
+        <v>60</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
+        <v>200</v>
+      </c>
+      <c r="G11" s="7">
+        <v>40</v>
+      </c>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="6">
-        <v>45</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="B12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7">
+        <v>200</v>
+      </c>
+      <c r="G12" s="7">
+        <v>40</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="6">
-        <v>35</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="6">
-        <v>30</v>
-      </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6">
-        <v>200</v>
-      </c>
-      <c r="G6" s="6">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="6">
-        <v>50</v>
-      </c>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>200</v>
-      </c>
-      <c r="G8" s="6">
-        <v>30</v>
-      </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="6">
-        <v>35</v>
-      </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="6">
-        <v>200</v>
-      </c>
-      <c r="G10" s="6">
-        <v>60</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="6">
-        <v>200</v>
-      </c>
-      <c r="G11" s="6">
-        <v>40</v>
-      </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6">
-        <v>200</v>
-      </c>
-      <c r="G12" s="6">
-        <v>40</v>
-      </c>
-      <c r="H12" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1655,27 +1697,27 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2">
@@ -1693,13 +1735,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>

--- a/Ability stat sheet.xlsx
+++ b/Ability stat sheet.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25254" windowHeight="10473"/>
+    <workbookView windowWidth="25254" windowHeight="10473" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Ability" sheetId="1" r:id="rId1"/>
     <sheet name="Enemies" sheetId="2" r:id="rId2"/>
+    <sheet name="Debuff" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -777,7 +778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -791,9 +792,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1370,7 +1368,7 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -1378,296 +1376,296 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>45</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>35</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>30</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>200</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>45</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>50</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>200</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>30</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>35</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>200</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>60</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>200</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>40</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>200</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>40</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
     </row>
@@ -1769,4 +1767,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.99082568807339" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Ability stat sheet.xlsx
+++ b/Ability stat sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25254" windowHeight="10473" activeTab="2"/>
+    <workbookView windowWidth="25254" windowHeight="9767"/>
   </bookViews>
   <sheets>
     <sheet name="Ability" sheetId="1" r:id="rId1"/>

--- a/Ability stat sheet.xlsx
+++ b/Ability stat sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25254" windowHeight="10473"/>
+    <workbookView windowWidth="25254" windowHeight="10473" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ability" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>No.</t>
   </si>
@@ -85,67 +85,70 @@
     <t>projectile</t>
   </si>
   <si>
+    <t>Fire arrow</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>applier</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>Ignition uppercut</t>
+  </si>
+  <si>
+    <t>applier,executioner</t>
+  </si>
+  <si>
+    <t>Aerial</t>
+  </si>
+  <si>
+    <t>Stomp</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Sharpshooter</t>
+  </si>
+  <si>
+    <t>executioner</t>
+  </si>
+  <si>
+    <t>Ice bolt</t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>Sledgehammer</t>
+  </si>
+  <si>
+    <t>Backstab</t>
+  </si>
+  <si>
+    <t>stylish</t>
+  </si>
+  <si>
+    <t>1,0.5</t>
+  </si>
+  <si>
+    <t>Double the trouble</t>
+  </si>
+  <si>
+    <t>(?)</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
     <t>Reserve</t>
   </si>
   <si>
     <t>utils</t>
-  </si>
-  <si>
-    <t>Fire arrow</t>
-  </si>
-  <si>
-    <t>range</t>
-  </si>
-  <si>
-    <t>applier</t>
-  </si>
-  <si>
-    <t>Burn</t>
-  </si>
-  <si>
-    <t>Ignition uppercut</t>
-  </si>
-  <si>
-    <t>applier,executioner</t>
-  </si>
-  <si>
-    <t>Aerial</t>
-  </si>
-  <si>
-    <t>Stomp</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>Sharpshooter</t>
-  </si>
-  <si>
-    <t>executioner</t>
-  </si>
-  <si>
-    <t>Ice bolt</t>
-  </si>
-  <si>
-    <t>Freeze</t>
-  </si>
-  <si>
-    <t>Sledgehammer</t>
-  </si>
-  <si>
-    <t>Backstab</t>
-  </si>
-  <si>
-    <t>stylish</t>
-  </si>
-  <si>
-    <t>1,0.5</t>
-  </si>
-  <si>
-    <t>Double the trouble</t>
-  </si>
-  <si>
-    <t>(?)</t>
   </si>
   <si>
     <t>Max reach</t>
@@ -340,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +353,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,7 +681,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -696,16 +705,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -714,89 +723,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -821,11 +830,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1360,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="8.99082568807339" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.23853211009174" customWidth="1"/>
@@ -1398,7 +1410,7 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1425,10 +1437,10 @@
         <v>45</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1455,10 +1467,10 @@
         <v>35</v>
       </c>
       <c r="H3" s="6"/>
-      <c r="I3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="9"/>
+      <c r="I3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="6">
@@ -1471,79 +1483,81 @@
         <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>13</v>
+      <c r="G4" s="6">
+        <v>30</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="I4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="9"/>
+      <c r="I4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="F5" s="6">
+        <v>200</v>
       </c>
       <c r="G5" s="6">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="9"/>
+      <c r="I5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6">
+        <v>50</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6">
-        <v>200</v>
-      </c>
-      <c r="G6" s="6">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>15</v>
+      <c r="J6" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1557,24 +1571,22 @@
         <v>11</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="F7" s="6">
+        <v>200</v>
       </c>
       <c r="G7" s="6">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="9">
-        <v>2</v>
-      </c>
+      <c r="I7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="6">
@@ -1584,25 +1596,25 @@
         <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="6">
-        <v>200</v>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="9"/>
+      <c r="I8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="6">
@@ -1612,54 +1624,56 @@
         <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="6">
+        <v>200</v>
       </c>
       <c r="G9" s="6">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="9"/>
+      <c r="I9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="6">
         <v>200</v>
       </c>
       <c r="G10" s="6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>15</v>
+      <c r="J10" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1667,16 +1681,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F11" s="6">
         <v>200</v>
@@ -1685,41 +1699,16 @@
         <v>40</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" s="6">
         <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="6">
-        <v>200</v>
-      </c>
-      <c r="G12" s="6">
-        <v>40</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -1751,6 +1740,45 @@
       <c r="A18" s="6">
         <v>17</v>
       </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1778,19 +1806,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1798,14 +1826,14 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2">
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2">
         <v>10</v>
@@ -1816,10 +1844,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
@@ -1828,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F3" s="2">
         <v>10</v>

--- a/Ability stat sheet.xlsx
+++ b/Ability stat sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25254" windowHeight="10473" activeTab="1"/>
+    <workbookView windowWidth="25254" windowHeight="9767"/>
   </bookViews>
   <sheets>
     <sheet name="Ability" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
   <si>
     <t>No.</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Setup</t>
   </si>
   <si>
+    <t>Excution</t>
+  </si>
+  <si>
     <t>Crit mult(%)</t>
   </si>
   <si>
@@ -133,13 +136,16 @@
     <t>stylish</t>
   </si>
   <si>
+    <t>Hit from back</t>
+  </si>
+  <si>
     <t>1,0.5</t>
   </si>
   <si>
     <t>Double the trouble</t>
   </si>
   <si>
-    <t>(?)</t>
+    <t>Mark for tomorrow</t>
   </si>
   <si>
     <t>Unused</t>
@@ -805,7 +811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -822,6 +828,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1372,17 +1384,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="8.99082568807339" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.23853211009174" customWidth="1"/>
     <col min="2" max="2" width="23.0550458715596" customWidth="1"/>
     <col min="4" max="4" width="17.9449541284404" customWidth="1"/>
-    <col min="6" max="6" width="11.2201834862385" customWidth="1"/>
+    <col min="5" max="5" width="19.1834862385321" customWidth="1"/>
+    <col min="6" max="6" width="16.0275229357798" customWidth="1"/>
+    <col min="7" max="7" width="11.9633027522936" customWidth="1"/>
     <col min="8" max="8" width="15.697247706422" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1398,7 +1412,7 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -1410,375 +1424,409 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="6">
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="7">
+        <v>45</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="7">
+        <v>35</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="7">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7">
+        <v>200</v>
+      </c>
+      <c r="H5" s="7">
+        <v>45</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="7">
+        <v>50</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7">
+        <v>200</v>
+      </c>
+      <c r="H7" s="7">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="7">
+        <v>35</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="7">
+        <v>200</v>
+      </c>
+      <c r="H9" s="7">
+        <v>60</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="7">
+        <v>200</v>
+      </c>
+      <c r="H10" s="7">
+        <v>40</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="7">
+        <v>200</v>
+      </c>
+      <c r="H11" s="7">
+        <v>40</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6">
-        <v>45</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6">
-        <v>35</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="6">
-        <v>30</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="6">
-        <v>200</v>
-      </c>
-      <c r="G5" s="6">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="6">
-        <v>50</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="6">
-        <v>200</v>
-      </c>
-      <c r="G7" s="6">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6">
-        <v>35</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="6">
-        <v>200</v>
-      </c>
-      <c r="G9" s="6">
-        <v>60</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="6">
-        <v>200</v>
-      </c>
-      <c r="G10" s="6">
-        <v>40</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="6">
-        <v>200</v>
-      </c>
-      <c r="G11" s="6">
-        <v>40</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="6"/>
+      <c r="E22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1806,27 +1854,27 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2">
@@ -1844,13 +1892,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
